--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00777B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00777B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7ED5E4B-6F2C-4734-B2A6-4FD1294F18EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0634D42-602D-41BB-B2A5-75A7D44CA564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E88834FF-C6E0-4528-856E-D17D0D5AE76A}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{9EA27B84-8C21-476D-BDA7-430EFE3B9501}"/>
   </bookViews>
   <sheets>
     <sheet name="00777B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1651,24 +1651,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A093E09-693F-4583-8973-BCD14744D4E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBD33E0-5E68-450A-B16C-FDA9EA053425}">
   <dimension ref="A1:R51"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1696,7 +1697,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1726,7 +1727,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1822,7 +1823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1876,7 +1877,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1902,7 +1903,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1958,7 +1959,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -2014,7 +2015,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2068,7 +2069,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2124,7 +2125,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2180,7 +2181,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2292,7 +2293,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2348,7 +2349,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2404,7 +2405,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2460,7 +2461,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2684,7 +2685,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2740,7 +2741,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2794,7 +2795,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2850,7 +2851,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2906,7 +2907,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2962,7 +2963,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -3018,7 +3019,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="49">
         <v>2023</v>
       </c>
@@ -3072,7 +3073,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>26</v>
       </c>
@@ -3128,7 +3129,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>26</v>
       </c>
@@ -3184,7 +3185,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>26</v>
       </c>
@@ -3240,7 +3241,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>26</v>
       </c>
@@ -3296,7 +3297,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="51">
         <v>2022</v>
       </c>
@@ -3350,7 +3351,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>26</v>
       </c>
@@ -3406,7 +3407,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3462,7 +3463,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>26</v>
       </c>
@@ -3518,7 +3519,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3574,7 +3575,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="49">
         <v>2021</v>
       </c>
@@ -3628,7 +3629,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>26</v>
       </c>
@@ -3684,7 +3685,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>26</v>
       </c>
@@ -3740,7 +3741,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>26</v>
       </c>
@@ -3796,7 +3797,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>26</v>
       </c>
@@ -3852,7 +3853,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="51">
         <v>2020</v>
       </c>
@@ -3906,7 +3907,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>26</v>
       </c>
@@ -3962,7 +3963,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>26</v>
       </c>
@@ -4018,7 +4019,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>26</v>
       </c>
@@ -4074,7 +4075,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>26</v>
       </c>
@@ -4130,7 +4131,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="49">
         <v>2019</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>26</v>
       </c>
@@ -4240,7 +4241,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>26</v>
       </c>
@@ -4296,7 +4297,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>26</v>
       </c>
@@ -4352,7 +4353,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="51" t="s">
         <v>88</v>
       </c>
